--- a/4_tables/2_meta_analysis/meta_housing_meta_analysis.xlsx
+++ b/4_tables/2_meta_analysis/meta_housing_meta_analysis.xlsx
@@ -1575,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AH31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1626,90 +1626,125 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>bc_estimate</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>pet_status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>peese_status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fit_status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>fit_note</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pet_term</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>model_formula</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>estimate_rr</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>std_error</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>statistic</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>conf_low</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>conf_high</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>conf_low_rr</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>conf_high_rr</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>pet_term_estimate</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pet_term_p_value</t>
         </is>
@@ -1749,68 +1784,88 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J2">
+        <v>-0.0441289342241922</v>
+      </c>
+      <c r="K2">
+        <v>0.039294877575553</v>
+      </c>
+      <c r="L2">
+        <v>-1.123020020595424</v>
+      </c>
+      <c r="M2">
+        <v>0.2614289916605104</v>
+      </c>
+      <c r="N2">
+        <v>0.1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q2">
         <v>8.801475483338173E-05</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q2">
+      <c r="X2">
         <v>-0.0441289342241922</v>
       </c>
-      <c r="R2">
+      <c r="Y2">
         <v>0.956830581310828</v>
       </c>
-      <c r="S2">
+      <c r="Z2">
         <v>0.03929487743047507</v>
       </c>
-      <c r="T2">
+      <c r="AA2">
         <v>-1.12302002474165</v>
       </c>
-      <c r="U2">
+      <c r="AB2">
         <v>0.2643197630713425</v>
       </c>
-      <c r="V2">
+      <c r="AC2">
         <v>-0.1211454787648392</v>
       </c>
-      <c r="W2">
+      <c r="AD2">
         <v>0.03288761031645475</v>
       </c>
-      <c r="X2">
+      <c r="AE2">
         <v>0.8859050698424167</v>
       </c>
-      <c r="Y2">
+      <c r="AF2">
         <v>1.033434385350644</v>
       </c>
-      <c r="Z2">
+      <c r="AG2">
         <v>-2.171136979968024</v>
       </c>
-      <c r="AA2">
+      <c r="AH2">
         <v>8.801475483338173E-05</v>
       </c>
     </row>
@@ -1848,68 +1903,88 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J3">
+        <v>-0.0441289342241922</v>
+      </c>
+      <c r="K3">
+        <v>0.039294877575553</v>
+      </c>
+      <c r="L3">
+        <v>-1.123020020595424</v>
+      </c>
+      <c r="M3">
+        <v>0.2614289916605104</v>
+      </c>
+      <c r="N3">
+        <v>0.1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q3">
         <v>8.801475483338173E-05</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q3">
+      <c r="X3">
         <v>-0.09483426427679595</v>
       </c>
-      <c r="R3">
+      <c r="Y3">
         <v>0.9095236625393556</v>
       </c>
-      <c r="S3">
+      <c r="Z3">
         <v>0.04271964348708504</v>
       </c>
-      <c r="T3">
+      <c r="AA3">
         <v>-2.219921716000887</v>
       </c>
-      <c r="U3">
+      <c r="AB3">
         <v>0.02885430705018921</v>
       </c>
-      <c r="V3">
+      <c r="AC3">
         <v>-0.1785632269438737</v>
       </c>
-      <c r="W3">
+      <c r="AD3">
         <v>-0.0111053016097182</v>
       </c>
-      <c r="X3">
+      <c r="AE3">
         <v>0.8364711676898278</v>
       </c>
-      <c r="Y3">
+      <c r="AF3">
         <v>0.9889561346192752</v>
       </c>
-      <c r="Z3">
+      <c r="AG3">
         <v>-6.964456385847269</v>
       </c>
-      <c r="AA3">
+      <c r="AH3">
         <v>0.009633536968474372</v>
       </c>
     </row>
@@ -1951,64 +2026,84 @@
         </is>
       </c>
       <c r="J4">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="K4">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="L4">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="M4">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="N4">
+        <v>0.1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q4">
         <v>0.6896331316971431</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q4">
+      <c r="X4">
         <v>0.01886571046568258</v>
       </c>
-      <c r="R4">
+      <c r="Y4">
         <v>1.019044792377816</v>
       </c>
-      <c r="S4">
+      <c r="Z4">
         <v>0.04777190240922339</v>
       </c>
-      <c r="T4">
+      <c r="AA4">
         <v>0.3949122709009</v>
       </c>
-      <c r="U4">
+      <c r="AB4">
         <v>0.6960102049424469</v>
       </c>
-      <c r="V4">
+      <c r="AC4">
         <v>-0.07476549772935748</v>
       </c>
-      <c r="W4">
+      <c r="AD4">
         <v>0.1124969186607226</v>
       </c>
-      <c r="X4">
+      <c r="AE4">
         <v>0.9279610697935819</v>
       </c>
-      <c r="Y4">
+      <c r="AF4">
         <v>1.119068808676794</v>
       </c>
-      <c r="Z4">
+      <c r="AG4">
         <v>0.2119180839801686</v>
       </c>
-      <c r="AA4">
+      <c r="AH4">
         <v>0.6896331316971431</v>
       </c>
     </row>
@@ -2050,64 +2145,84 @@
         </is>
       </c>
       <c r="J5">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="K5">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="L5">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="M5">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="N5">
+        <v>0.1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q5">
         <v>0.6896331316971431</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q5">
+      <c r="X5">
         <v>0.03131978135066973</v>
       </c>
-      <c r="R5">
+      <c r="Y5">
         <v>1.031815406459686</v>
       </c>
-      <c r="S5">
+      <c r="Z5">
         <v>0.02716655728340297</v>
       </c>
-      <c r="T5">
+      <c r="AA5">
         <v>1.152880029071778</v>
       </c>
-      <c r="U5">
+      <c r="AB5">
         <v>0.2590645663043031</v>
       </c>
-      <c r="V5">
+      <c r="AC5">
         <v>-0.02192569250874436</v>
       </c>
-      <c r="W5">
+      <c r="AD5">
         <v>0.08456525521008382</v>
       </c>
-      <c r="X5">
+      <c r="AE5">
         <v>0.9783129283297162</v>
       </c>
-      <c r="Y5">
+      <c r="AF5">
         <v>1.088243855496464</v>
       </c>
-      <c r="Z5">
+      <c r="AG5">
         <v>-0.04395662933434719</v>
       </c>
-      <c r="AA5">
+      <c r="AH5">
         <v>0.9509504190273802</v>
       </c>
     </row>
@@ -2145,68 +2260,88 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J6">
+        <v>-0.01623317719789098</v>
+      </c>
+      <c r="K6">
+        <v>0.01085249306634288</v>
+      </c>
+      <c r="L6">
+        <v>-1.495801664986579</v>
+      </c>
+      <c r="M6">
+        <v>0.1347053473598521</v>
+      </c>
+      <c r="N6">
+        <v>0.1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q6">
         <v>0.00152539740558465</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q6">
+      <c r="X6">
         <v>-0.01623317719789098</v>
       </c>
-      <c r="R6">
+      <c r="Y6">
         <v>0.9838978707566386</v>
       </c>
-      <c r="S6">
+      <c r="Z6">
         <v>0.01085249309360055</v>
       </c>
-      <c r="T6">
+      <c r="AA6">
         <v>-1.495801661229649</v>
       </c>
-      <c r="U6">
+      <c r="AB6">
         <v>0.1585823524778318</v>
       </c>
-      <c r="V6">
+      <c r="AC6">
         <v>-0.03750367280381772</v>
       </c>
-      <c r="W6">
+      <c r="AD6">
         <v>0.005037318408035753</v>
       </c>
-      <c r="X6">
+      <c r="AE6">
         <v>0.9631908801031837</v>
       </c>
-      <c r="Y6">
+      <c r="AF6">
         <v>1.005050027026566</v>
       </c>
-      <c r="Z6">
+      <c r="AG6">
         <v>-2.105870116707555</v>
       </c>
-      <c r="AA6">
+      <c r="AH6">
         <v>0.00152539740558465</v>
       </c>
     </row>
@@ -2244,68 +2379,88 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J7">
+        <v>-0.01623317719789098</v>
+      </c>
+      <c r="K7">
+        <v>0.01085249306634288</v>
+      </c>
+      <c r="L7">
+        <v>-1.495801664986579</v>
+      </c>
+      <c r="M7">
+        <v>0.1347053473598521</v>
+      </c>
+      <c r="N7">
+        <v>0.1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q7">
         <v>0.00152539740558465</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q7">
+      <c r="X7">
         <v>-0.04736005941814025</v>
       </c>
-      <c r="R7">
+      <c r="Y7">
         <v>0.9537439312749914</v>
       </c>
-      <c r="S7">
+      <c r="Z7">
         <v>0.01394608033199637</v>
       </c>
-      <c r="T7">
+      <c r="AA7">
         <v>-3.395940528858311</v>
       </c>
-      <c r="U7">
+      <c r="AB7">
         <v>0.004779457142527119</v>
       </c>
-      <c r="V7">
+      <c r="AC7">
         <v>-0.07469387459435553</v>
       </c>
-      <c r="W7">
+      <c r="AD7">
         <v>-0.02002624424192496</v>
       </c>
-      <c r="X7">
+      <c r="AE7">
         <v>0.9280275356547786</v>
       </c>
-      <c r="Y7">
+      <c r="AF7">
         <v>0.9801729490731965</v>
       </c>
-      <c r="Z7">
+      <c r="AG7">
         <v>-9.791893465386963</v>
       </c>
-      <c r="AA7">
+      <c r="AH7">
         <v>0.02225205193640684</v>
       </c>
     </row>
@@ -2347,64 +2502,84 @@
         </is>
       </c>
       <c r="J8">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="K8">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="L8">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="M8">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="N8">
+        <v>0.1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q8">
         <v>0.2130269863307577</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q8">
+      <c r="X8">
         <v>-0.01650615869253858</v>
       </c>
-      <c r="R8">
+      <c r="Y8">
         <v>0.983629321501455</v>
       </c>
-      <c r="S8">
+      <c r="Z8">
         <v>0.0267672554654336</v>
       </c>
-      <c r="T8">
+      <c r="AA8">
         <v>-0.6166548794609935</v>
       </c>
-      <c r="U8">
+      <c r="AB8">
         <v>0.5456327536525746</v>
       </c>
-      <c r="V8">
+      <c r="AC8">
         <v>-0.06896901536977135</v>
       </c>
-      <c r="W8">
+      <c r="AD8">
         <v>0.03595669798469419</v>
       </c>
-      <c r="X8">
+      <c r="AE8">
         <v>0.9333555993082903</v>
       </c>
-      <c r="Y8">
+      <c r="AF8">
         <v>1.036610958175476</v>
       </c>
-      <c r="Z8">
+      <c r="AG8">
         <v>-0.4058176217004146</v>
       </c>
-      <c r="AA8">
+      <c r="AH8">
         <v>0.2130269863307577</v>
       </c>
     </row>
@@ -2446,64 +2621,84 @@
         </is>
       </c>
       <c r="J9">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="K9">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="L9">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="M9">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="N9">
+        <v>0.1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q9">
         <v>0.2130269863307577</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q9">
+      <c r="X9">
         <v>-0.03475110777132287</v>
       </c>
-      <c r="R9">
+      <c r="Y9">
         <v>0.9658457778524673</v>
       </c>
-      <c r="S9">
+      <c r="Z9">
         <v>0.0208940689016761</v>
       </c>
-      <c r="T9">
+      <c r="AA9">
         <v>-1.663204421065883</v>
       </c>
-      <c r="U9">
+      <c r="AB9">
         <v>0.1145959988842152</v>
       </c>
-      <c r="V9">
+      <c r="AC9">
         <v>-0.07570273030910638</v>
       </c>
-      <c r="W9">
+      <c r="AD9">
         <v>0.006200514766460642</v>
       </c>
-      <c r="X9">
+      <c r="AE9">
         <v>0.9270917618817148</v>
       </c>
-      <c r="Y9">
+      <c r="AF9">
         <v>1.006219777751038</v>
       </c>
-      <c r="Z9">
+      <c r="AG9">
         <v>-1.396296029967288</v>
       </c>
-      <c r="AA9">
+      <c r="AH9">
         <v>0.214592197779984</v>
       </c>
     </row>
@@ -2545,64 +2740,84 @@
         </is>
       </c>
       <c r="J10">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="K10">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="L10">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="M10">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="N10">
+        <v>0.1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q10">
         <v>0.3518414027608091</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q10">
+      <c r="X10">
         <v>-0.1514253255935879</v>
       </c>
-      <c r="R10">
+      <c r="Y10">
         <v>0.8594820611893771</v>
       </c>
-      <c r="S10">
+      <c r="Z10">
         <v>0.1500586842514219</v>
       </c>
-      <c r="T10">
+      <c r="AA10">
         <v>-1.009107379216228</v>
       </c>
-      <c r="U10">
+      <c r="AB10">
         <v>0.3238937376980864</v>
       </c>
-      <c r="V10">
+      <c r="AC10">
         <v>-0.4455349422938426</v>
       </c>
-      <c r="W10">
+      <c r="AD10">
         <v>0.1426842911066667</v>
       </c>
-      <c r="X10">
+      <c r="AE10">
         <v>0.6404815636979818</v>
       </c>
-      <c r="Y10">
+      <c r="AF10">
         <v>1.15336561639841</v>
       </c>
-      <c r="Z10">
+      <c r="AG10">
         <v>-1.66112279063935</v>
       </c>
-      <c r="AA10">
+      <c r="AH10">
         <v>0.3518414027608091</v>
       </c>
     </row>
@@ -2644,64 +2859,84 @@
         </is>
       </c>
       <c r="J11">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="K11">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="L11">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="M11">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="N11">
+        <v>0.1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q11">
         <v>0.3518414027608091</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q11">
+      <c r="X11">
         <v>-0.2242916600288756</v>
       </c>
-      <c r="R11">
+      <c r="Y11">
         <v>0.799082040087989</v>
       </c>
-      <c r="S11">
+      <c r="Z11">
         <v>0.09826985522522132</v>
       </c>
-      <c r="T11">
+      <c r="AA11">
         <v>-2.282405520134626</v>
       </c>
-      <c r="U11">
+      <c r="AB11">
         <v>0.03249341269935009</v>
       </c>
-      <c r="V11">
+      <c r="AC11">
         <v>-0.4168970370362746</v>
       </c>
-      <c r="W11">
+      <c r="AD11">
         <v>-0.03168628302147664</v>
       </c>
-      <c r="X11">
+      <c r="AE11">
         <v>0.659088778184578</v>
       </c>
-      <c r="Y11">
+      <c r="AF11">
         <v>0.9688104667021981</v>
       </c>
-      <c r="Z11">
+      <c r="AG11">
         <v>-4.972052776093125</v>
       </c>
-      <c r="AA11">
+      <c r="AH11">
         <v>0.3794738080197116</v>
       </c>
     </row>
@@ -2744,68 +2979,88 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="J12">
+        <v>-0.2280248923827685</v>
+      </c>
+      <c r="K12">
+        <v>0.05623988471185582</v>
+      </c>
+      <c r="L12">
+        <v>-4.054504975446704</v>
+      </c>
+      <c r="M12">
+        <v>5.02405812419616E-05</v>
+      </c>
+      <c r="N12">
+        <v>0.1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q12">
         <v>0.1061267217701378</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q12">
+      <c r="X12">
         <v>-0.2280248923827685</v>
       </c>
-      <c r="R12">
+      <c r="Y12">
         <v>0.7961044426522961</v>
       </c>
-      <c r="S12">
+      <c r="Z12">
         <v>0.05623988514012759</v>
       </c>
-      <c r="T12">
+      <c r="AA12">
         <v>-4.054504944571285</v>
       </c>
-      <c r="U12">
+      <c r="AB12">
         <v>0.0001687235753945533</v>
       </c>
-      <c r="V12">
+      <c r="AC12">
         <v>-0.3382530417520879</v>
       </c>
-      <c r="W12">
+      <c r="AD12">
         <v>-0.117796743013449</v>
       </c>
-      <c r="X12">
+      <c r="AE12">
         <v>0.7130148425441187</v>
       </c>
-      <c r="Y12">
+      <c r="AF12">
         <v>0.8888767046550042</v>
       </c>
-      <c r="Z12">
+      <c r="AG12">
         <v>-1.018234177038682</v>
       </c>
-      <c r="AA12">
+      <c r="AH12">
         <v>0.1061267217701378</v>
       </c>
     </row>
@@ -2848,68 +3103,88 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="J13">
+        <v>-0.2280248923827685</v>
+      </c>
+      <c r="K13">
+        <v>0.05623988471185582</v>
+      </c>
+      <c r="L13">
+        <v>-4.054504975446704</v>
+      </c>
+      <c r="M13">
+        <v>5.02405812419616E-05</v>
+      </c>
+      <c r="N13">
+        <v>0.1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q13">
         <v>0.1061267217701378</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q13">
+      <c r="X13">
         <v>-0.2598660612944457</v>
       </c>
-      <c r="R13">
+      <c r="Y13">
         <v>0.7711548663713628</v>
       </c>
-      <c r="S13">
+      <c r="Z13">
         <v>0.03328198001093026</v>
       </c>
-      <c r="T13">
+      <c r="AA13">
         <v>-7.80801085780059</v>
       </c>
-      <c r="U13">
+      <c r="AB13">
         <v>2.562752350564518E-10</v>
       </c>
-      <c r="V13">
+      <c r="AC13">
         <v>-0.3250975434500509</v>
       </c>
-      <c r="W13">
+      <c r="AD13">
         <v>-0.1946345791388404</v>
       </c>
-      <c r="X13">
+      <c r="AE13">
         <v>0.7224568792684545</v>
       </c>
-      <c r="Y13">
+      <c r="AF13">
         <v>0.8231353939495953</v>
       </c>
-      <c r="Z13">
+      <c r="AG13">
         <v>-4.931118471925302</v>
       </c>
-      <c r="AA13">
+      <c r="AH13">
         <v>0.01784479789143678</v>
       </c>
     </row>
@@ -2952,68 +3227,88 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J14">
+        <v>-0.01398931214936958</v>
+      </c>
+      <c r="K14">
+        <v>0.02801957205396191</v>
+      </c>
+      <c r="L14">
+        <v>-0.4992693008454251</v>
+      </c>
+      <c r="M14">
+        <v>0.6175896790784481</v>
+      </c>
+      <c r="N14">
+        <v>0.1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q14">
         <v>0.06140889364563524</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q14">
+      <c r="X14">
         <v>-0.01398931214936958</v>
       </c>
-      <c r="R14">
+      <c r="Y14">
         <v>0.9861080835824433</v>
       </c>
-      <c r="S14">
+      <c r="Z14">
         <v>0.02801957213560818</v>
       </c>
-      <c r="T14">
+      <c r="AA14">
         <v>-0.4992692993906037</v>
       </c>
-      <c r="U14">
+      <c r="AB14">
         <v>0.6283901339179836</v>
       </c>
-      <c r="V14">
+      <c r="AC14">
         <v>-0.06890666439738365</v>
       </c>
-      <c r="W14">
+      <c r="AD14">
         <v>0.04092804009864449</v>
       </c>
-      <c r="X14">
+      <c r="AE14">
         <v>0.9334137967518054</v>
       </c>
-      <c r="Y14">
+      <c r="AF14">
         <v>1.041777136668146</v>
       </c>
-      <c r="Z14">
+      <c r="AG14">
         <v>-1.438915400305928</v>
       </c>
-      <c r="AA14">
+      <c r="AH14">
         <v>0.06140889364563524</v>
       </c>
     </row>
@@ -3056,68 +3351,88 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J15">
+        <v>-0.01398931214936958</v>
+      </c>
+      <c r="K15">
+        <v>0.02801957205396191</v>
+      </c>
+      <c r="L15">
+        <v>-0.4992693008454251</v>
+      </c>
+      <c r="M15">
+        <v>0.6175896790784481</v>
+      </c>
+      <c r="N15">
+        <v>0.1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q15">
         <v>0.06140889364563524</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q15">
+      <c r="X15">
         <v>-0.04104926192869048</v>
       </c>
-      <c r="R15">
+      <c r="Y15">
         <v>0.959781848078252</v>
       </c>
-      <c r="S15">
+      <c r="Z15">
         <v>0.0414834596191135</v>
       </c>
-      <c r="T15">
+      <c r="AA15">
         <v>-0.9895332333800104</v>
       </c>
-      <c r="U15">
+      <c r="AB15">
         <v>0.3457406751163927</v>
       </c>
-      <c r="V15">
+      <c r="AC15">
         <v>-0.1223553487362746</v>
       </c>
-      <c r="W15">
+      <c r="AD15">
         <v>0.04025682487889364</v>
       </c>
-      <c r="X15">
+      <c r="AE15">
         <v>0.8848338880268932</v>
       </c>
-      <c r="Y15">
+      <c r="AF15">
         <v>1.041078114621789</v>
       </c>
-      <c r="Z15">
+      <c r="AG15">
         <v>-4.988835520931911</v>
       </c>
-      <c r="AA15">
+      <c r="AH15">
         <v>0.04171936190697131</v>
       </c>
     </row>
@@ -3160,68 +3475,88 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J16">
+        <v>-0.01300522048704099</v>
+      </c>
+      <c r="K16">
+        <v>0.02317731125588256</v>
+      </c>
+      <c r="L16">
+        <v>-0.5611186018714822</v>
+      </c>
+      <c r="M16">
+        <v>0.5747166878669911</v>
+      </c>
+      <c r="N16">
+        <v>0.1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q16">
         <v>3.648344743013438E-07</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q16">
+      <c r="X16">
         <v>-0.01300522048704099</v>
       </c>
-      <c r="R16">
+      <c r="Y16">
         <v>0.9870789819738031</v>
       </c>
-      <c r="S16">
+      <c r="Z16">
         <v>0.0231773111185831</v>
       </c>
-      <c r="T16">
+      <c r="AA16">
         <v>-0.5611186051954777</v>
       </c>
-      <c r="U16">
+      <c r="AB16">
         <v>0.578750576522196</v>
       </c>
-      <c r="V16">
+      <c r="AC16">
         <v>-0.05843191553794361</v>
       </c>
-      <c r="W16">
+      <c r="AD16">
         <v>0.03242147456386164</v>
       </c>
-      <c r="X16">
+      <c r="AE16">
         <v>0.9432424583688857</v>
       </c>
-      <c r="Y16">
+      <c r="AF16">
         <v>1.032952776891854</v>
       </c>
-      <c r="Z16">
+      <c r="AG16">
         <v>-2.634695400220785</v>
       </c>
-      <c r="AA16">
+      <c r="AH16">
         <v>3.648344743013438E-07</v>
       </c>
     </row>
@@ -3264,68 +3599,88 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J17">
+        <v>-0.01300522048704099</v>
+      </c>
+      <c r="K17">
+        <v>0.02317731125588256</v>
+      </c>
+      <c r="L17">
+        <v>-0.5611186018714822</v>
+      </c>
+      <c r="M17">
+        <v>0.5747166878669911</v>
+      </c>
+      <c r="N17">
+        <v>0.1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q17">
         <v>3.648344743013438E-07</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q17">
+      <c r="X17">
         <v>-0.05867009048934309</v>
       </c>
-      <c r="R17">
+      <c r="Y17">
         <v>0.9430178283938843</v>
       </c>
-      <c r="S17">
+      <c r="Z17">
         <v>0.03259294229560664</v>
       </c>
-      <c r="T17">
+      <c r="AA17">
         <v>-1.800085735041219</v>
       </c>
-      <c r="U17">
+      <c r="AB17">
         <v>0.08158614487495558</v>
       </c>
-      <c r="V17">
+      <c r="AC17">
         <v>-0.1225510835389243</v>
       </c>
-      <c r="W17">
+      <c r="AD17">
         <v>0.00521090256023813</v>
       </c>
-      <c r="X17">
+      <c r="AE17">
         <v>0.8846607121892646</v>
       </c>
-      <c r="Y17">
+      <c r="AF17">
         <v>1.005224502926116</v>
       </c>
-      <c r="Z17">
+      <c r="AG17">
         <v>-13.28632606558108</v>
       </c>
-      <c r="AA17">
+      <c r="AH17">
         <v>0.0003475644117808953</v>
       </c>
     </row>
@@ -3368,68 +3723,88 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="J18">
+        <v>-0.2071747835899547</v>
+      </c>
+      <c r="K18">
+        <v>0.1133988387623222</v>
+      </c>
+      <c r="L18">
+        <v>-1.826956835282783</v>
+      </c>
+      <c r="M18">
+        <v>0.0677062596835441</v>
+      </c>
+      <c r="N18">
+        <v>0.1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q18">
         <v>0.8755791713346561</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q18">
+      <c r="X18">
         <v>-0.2071747835899547</v>
       </c>
-      <c r="R18">
+      <c r="Y18">
         <v>0.8128775599123109</v>
       </c>
-      <c r="S18">
+      <c r="Z18">
         <v>0.1133988387718463</v>
       </c>
-      <c r="T18">
+      <c r="AA18">
         <v>-1.826956835129341</v>
       </c>
-      <c r="U18">
+      <c r="AB18">
         <v>0.08130569386996259</v>
       </c>
-      <c r="V18">
+      <c r="AC18">
         <v>-0.4294324234714377</v>
       </c>
-      <c r="W18">
+      <c r="AD18">
         <v>0.01508285629152831</v>
       </c>
-      <c r="X18">
+      <c r="AE18">
         <v>0.6508784132154372</v>
       </c>
-      <c r="Y18">
+      <c r="AF18">
         <v>1.015197176604291</v>
       </c>
-      <c r="Z18">
+      <c r="AG18">
         <v>0.1876542705546367</v>
       </c>
-      <c r="AA18">
+      <c r="AH18">
         <v>0.8755791713346561</v>
       </c>
     </row>
@@ -3472,68 +3847,88 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="J19">
+        <v>-0.2071747835899547</v>
+      </c>
+      <c r="K19">
+        <v>0.1133988387623222</v>
+      </c>
+      <c r="L19">
+        <v>-1.826956835282783</v>
+      </c>
+      <c r="M19">
+        <v>0.0677062596835441</v>
+      </c>
+      <c r="N19">
+        <v>0.1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q19">
         <v>0.8755791713346561</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q19">
+      <c r="X19">
         <v>-0.1992084125040391</v>
       </c>
-      <c r="R19">
+      <c r="Y19">
         <v>0.8193791066851257</v>
       </c>
-      <c r="S19">
+      <c r="Z19">
         <v>0.07392677096711239</v>
       </c>
-      <c r="T19">
+      <c r="AA19">
         <v>-2.694672172177796</v>
       </c>
-      <c r="U19">
+      <c r="AB19">
         <v>0.01323585520137345</v>
       </c>
-      <c r="V19">
+      <c r="AC19">
         <v>-0.3441022210929207</v>
       </c>
-      <c r="W19">
+      <c r="AD19">
         <v>-0.05431460391515758</v>
       </c>
-      <c r="X19">
+      <c r="AE19">
         <v>0.7088564642634092</v>
       </c>
-      <c r="Y19">
+      <c r="AF19">
         <v>0.9471340875331721</v>
       </c>
-      <c r="Z19">
+      <c r="AG19">
         <v>-0.1863456442543887</v>
       </c>
-      <c r="AA19">
+      <c r="AH19">
         <v>0.8903727859390478</v>
       </c>
     </row>
@@ -3576,68 +3971,88 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J20">
+        <v>-0.002326701182641406</v>
+      </c>
+      <c r="K20">
+        <v>0.009419121958906233</v>
+      </c>
+      <c r="L20">
+        <v>-0.2470189039692174</v>
+      </c>
+      <c r="M20">
+        <v>0.8048935940809889</v>
+      </c>
+      <c r="N20">
+        <v>0.1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q20">
         <v>0.05791197033513358</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q20">
+      <c r="X20">
         <v>-0.002326701182641406</v>
       </c>
-      <c r="R20">
+      <c r="Y20">
         <v>0.9976760034884947</v>
       </c>
-      <c r="S20">
+      <c r="Z20">
         <v>0.009419121996543186</v>
       </c>
-      <c r="T20">
+      <c r="AA20">
         <v>-0.2470189029821786</v>
       </c>
-      <c r="U20">
+      <c r="AB20">
         <v>0.8090690395779558</v>
       </c>
-      <c r="V20">
+      <c r="AC20">
         <v>-0.02078784106185505</v>
       </c>
-      <c r="W20">
+      <c r="AD20">
         <v>0.01613443869657224</v>
       </c>
-      <c r="X20">
+      <c r="AE20">
         <v>0.9794267366647682</v>
       </c>
-      <c r="Y20">
+      <c r="AF20">
         <v>1.016265301605157</v>
       </c>
-      <c r="Z20">
+      <c r="AG20">
         <v>-0.948379600560244</v>
       </c>
-      <c r="AA20">
+      <c r="AH20">
         <v>0.05791197033513358</v>
       </c>
     </row>
@@ -3680,68 +4095,88 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J21">
+        <v>-0.002326701182641406</v>
+      </c>
+      <c r="K21">
+        <v>0.009419121958906233</v>
+      </c>
+      <c r="L21">
+        <v>-0.2470189039692174</v>
+      </c>
+      <c r="M21">
+        <v>0.8048935940809889</v>
+      </c>
+      <c r="N21">
+        <v>0.1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q21">
         <v>0.05791197033513358</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q21">
+      <c r="X21">
         <v>-0.01135694937232996</v>
       </c>
-      <c r="R21">
+      <c r="Y21">
         <v>0.9887072973316636</v>
       </c>
-      <c r="S21">
+      <c r="Z21">
         <v>0.01021621409258023</v>
       </c>
-      <c r="T21">
+      <c r="AA21">
         <v>-1.111659296625177</v>
       </c>
-      <c r="U21">
+      <c r="AB21">
         <v>0.2880608845387202</v>
       </c>
-      <c r="V21">
+      <c r="AC21">
         <v>-0.03138036105213775</v>
       </c>
-      <c r="W21">
+      <c r="AD21">
         <v>0.008666462307477833</v>
       </c>
-      <c r="X21">
+      <c r="AE21">
         <v>0.9691068924473497</v>
       </c>
-      <c r="Y21">
+      <c r="AF21">
         <v>1.00870412481355</v>
       </c>
-      <c r="Z21">
+      <c r="AG21">
         <v>-8.037711675485626</v>
       </c>
-      <c r="AA21">
+      <c r="AH21">
         <v>0.02518683488334981</v>
       </c>
     </row>
@@ -3784,68 +4219,88 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J22">
+        <v>0.01125249478786305</v>
+      </c>
+      <c r="K22">
+        <v>0.01867213013725901</v>
+      </c>
+      <c r="L22">
+        <v>0.6026358377510148</v>
+      </c>
+      <c r="M22">
+        <v>0.5467509738989856</v>
+      </c>
+      <c r="N22">
+        <v>0.1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q22">
         <v>0.001963325122337626</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q22">
+      <c r="X22">
         <v>0.01125249478786305</v>
       </c>
-      <c r="R22">
+      <c r="Y22">
         <v>1.011316042239452</v>
       </c>
-      <c r="S22">
+      <c r="Z22">
         <v>0.01867213018063969</v>
       </c>
-      <c r="T22">
+      <c r="AA22">
         <v>0.6026358363509199</v>
       </c>
-      <c r="U22">
+      <c r="AB22">
         <v>0.5579679180388102</v>
       </c>
-      <c r="V22">
+      <c r="AC22">
         <v>-0.02534420788083411</v>
       </c>
-      <c r="W22">
+      <c r="AD22">
         <v>0.04784919745656022</v>
       </c>
-      <c r="X22">
+      <c r="AE22">
         <v>0.9749742604406317</v>
       </c>
-      <c r="Y22">
+      <c r="AF22">
         <v>1.049012449650354</v>
       </c>
-      <c r="Z22">
+      <c r="AG22">
         <v>-2.976198166772118</v>
       </c>
-      <c r="AA22">
+      <c r="AH22">
         <v>0.001963325122337626</v>
       </c>
     </row>
@@ -3888,68 +4343,88 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J23">
+        <v>0.01125249478786305</v>
+      </c>
+      <c r="K23">
+        <v>0.01867213013725901</v>
+      </c>
+      <c r="L23">
+        <v>0.6026358377510148</v>
+      </c>
+      <c r="M23">
+        <v>0.5467509738989856</v>
+      </c>
+      <c r="N23">
+        <v>0.1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q23">
         <v>0.001963325122337626</v>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q23">
+      <c r="X23">
         <v>-0.06033396056904067</v>
       </c>
-      <c r="R23">
+      <c r="Y23">
         <v>0.9414500738762047</v>
       </c>
-      <c r="S23">
+      <c r="Z23">
         <v>0.01552697325646305</v>
       </c>
-      <c r="T23">
+      <c r="AA23">
         <v>-3.885751561008637</v>
       </c>
-      <c r="U23">
+      <c r="AB23">
         <v>0.002165206649137497</v>
       </c>
-      <c r="V23">
+      <c r="AC23">
         <v>-0.09076626894062485</v>
       </c>
-      <c r="W23">
+      <c r="AD23">
         <v>-0.0299016521974565</v>
       </c>
-      <c r="X23">
+      <c r="AE23">
         <v>0.9132311364371795</v>
       </c>
-      <c r="Y23">
+      <c r="AF23">
         <v>0.9705409794275901</v>
       </c>
-      <c r="Z23">
+      <c r="AG23">
         <v>-14.15774432702603</v>
       </c>
-      <c r="AA23">
+      <c r="AH23">
         <v>0.02523944556753687</v>
       </c>
     </row>
@@ -3996,64 +4471,84 @@
         </is>
       </c>
       <c r="J24">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="K24">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="L24">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="M24">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="N24">
+        <v>0.1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q24">
         <v>0.6896331316971431</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q24">
+      <c r="X24">
         <v>0.01886571046568258</v>
       </c>
-      <c r="R24">
+      <c r="Y24">
         <v>1.019044792377816</v>
       </c>
-      <c r="S24">
+      <c r="Z24">
         <v>0.04777190240922339</v>
       </c>
-      <c r="T24">
+      <c r="AA24">
         <v>0.3949122709009</v>
       </c>
-      <c r="U24">
+      <c r="AB24">
         <v>0.6960102049424469</v>
       </c>
-      <c r="V24">
+      <c r="AC24">
         <v>-0.07476549772935748</v>
       </c>
-      <c r="W24">
+      <c r="AD24">
         <v>0.1124969186607226</v>
       </c>
-      <c r="X24">
+      <c r="AE24">
         <v>0.9279610697935819</v>
       </c>
-      <c r="Y24">
+      <c r="AF24">
         <v>1.119068808676794</v>
       </c>
-      <c r="Z24">
+      <c r="AG24">
         <v>0.2119180839801686</v>
       </c>
-      <c r="AA24">
+      <c r="AH24">
         <v>0.6896331316971431</v>
       </c>
     </row>
@@ -4100,64 +4595,84 @@
         </is>
       </c>
       <c r="J25">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="K25">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="L25">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="M25">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="N25">
+        <v>0.1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q25">
         <v>0.6896331316971431</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q25">
+      <c r="X25">
         <v>0.03131978135066973</v>
       </c>
-      <c r="R25">
+      <c r="Y25">
         <v>1.031815406459686</v>
       </c>
-      <c r="S25">
+      <c r="Z25">
         <v>0.02716655728340297</v>
       </c>
-      <c r="T25">
+      <c r="AA25">
         <v>1.152880029071778</v>
       </c>
-      <c r="U25">
+      <c r="AB25">
         <v>0.2590645663043031</v>
       </c>
-      <c r="V25">
+      <c r="AC25">
         <v>-0.02192569250874436</v>
       </c>
-      <c r="W25">
+      <c r="AD25">
         <v>0.08456525521008382</v>
       </c>
-      <c r="X25">
+      <c r="AE25">
         <v>0.9783129283297162</v>
       </c>
-      <c r="Y25">
+      <c r="AF25">
         <v>1.088243855496464</v>
       </c>
-      <c r="Z25">
+      <c r="AG25">
         <v>-0.04395662933434719</v>
       </c>
-      <c r="AA25">
+      <c r="AH25">
         <v>0.9509504190273802</v>
       </c>
     </row>
@@ -4200,68 +4715,88 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J26">
+        <v>-0.01562270818073927</v>
+      </c>
+      <c r="K26">
+        <v>0.01140561087549029</v>
+      </c>
+      <c r="L26">
+        <v>-1.369738837427039</v>
+      </c>
+      <c r="M26">
+        <v>0.1707684405789152</v>
+      </c>
+      <c r="N26">
+        <v>0.1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q26">
         <v>0.009018500526151949</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q26">
+      <c r="X26">
         <v>-0.01562270818073927</v>
       </c>
-      <c r="R26">
+      <c r="Y26">
         <v>0.9844986932958903</v>
       </c>
-      <c r="S26">
+      <c r="Z26">
         <v>0.0114056109963859</v>
       </c>
-      <c r="T26">
+      <c r="AA26">
         <v>-1.369738822908273</v>
       </c>
-      <c r="U26">
+      <c r="AB26">
         <v>0.1980796049800176</v>
       </c>
-      <c r="V26">
+      <c r="AC26">
         <v>-0.03797729495532962</v>
       </c>
-      <c r="W26">
+      <c r="AD26">
         <v>0.006731878593851083</v>
       </c>
-      <c r="X26">
+      <c r="AE26">
         <v>0.9627347995796776</v>
       </c>
-      <c r="Y26">
+      <c r="AF26">
         <v>1.006754588620332</v>
       </c>
-      <c r="Z26">
+      <c r="AG26">
         <v>-2.053147716251145</v>
       </c>
-      <c r="AA26">
+      <c r="AH26">
         <v>0.009018500526151949</v>
       </c>
     </row>
@@ -4304,68 +4839,88 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J27">
+        <v>-0.01562270818073927</v>
+      </c>
+      <c r="K27">
+        <v>0.01140561087549029</v>
+      </c>
+      <c r="L27">
+        <v>-1.369738837427039</v>
+      </c>
+      <c r="M27">
+        <v>0.1707684405789152</v>
+      </c>
+      <c r="N27">
+        <v>0.1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q27">
         <v>0.009018500526151949</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q27">
+      <c r="X27">
         <v>-0.04417121364231996</v>
       </c>
-      <c r="R27">
+      <c r="Y27">
         <v>0.9567901279257822</v>
       </c>
-      <c r="S27">
+      <c r="Z27">
         <v>0.01182664939555682</v>
       </c>
-      <c r="T27">
+      <c r="AA27">
         <v>-3.734888231227583</v>
       </c>
-      <c r="U27">
+      <c r="AB27">
         <v>0.003295332952781328</v>
       </c>
-      <c r="V27">
+      <c r="AC27">
         <v>-0.06735102051539371</v>
       </c>
-      <c r="W27">
+      <c r="AD27">
         <v>-0.02099140676924621</v>
       </c>
-      <c r="X27">
+      <c r="AE27">
         <v>0.9348669862436952</v>
       </c>
-      <c r="Y27">
+      <c r="AF27">
         <v>0.9792273792601353</v>
       </c>
-      <c r="Z27">
+      <c r="AG27">
         <v>-9.163029094789252</v>
       </c>
-      <c r="AA27">
+      <c r="AH27">
         <v>0.04947294756578603</v>
       </c>
     </row>
@@ -4412,64 +4967,84 @@
         </is>
       </c>
       <c r="J28">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="K28">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="L28">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="M28">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="N28">
+        <v>0.1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q28">
         <v>0.2130269863307577</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q28">
+      <c r="X28">
         <v>-0.01650615869253858</v>
       </c>
-      <c r="R28">
+      <c r="Y28">
         <v>0.983629321501455</v>
       </c>
-      <c r="S28">
+      <c r="Z28">
         <v>0.0267672554654336</v>
       </c>
-      <c r="T28">
+      <c r="AA28">
         <v>-0.6166548794609935</v>
       </c>
-      <c r="U28">
+      <c r="AB28">
         <v>0.5456327536525746</v>
       </c>
-      <c r="V28">
+      <c r="AC28">
         <v>-0.06896901536977135</v>
       </c>
-      <c r="W28">
+      <c r="AD28">
         <v>0.03595669798469419</v>
       </c>
-      <c r="X28">
+      <c r="AE28">
         <v>0.9333555993082903</v>
       </c>
-      <c r="Y28">
+      <c r="AF28">
         <v>1.036610958175476</v>
       </c>
-      <c r="Z28">
+      <c r="AG28">
         <v>-0.4058176217004146</v>
       </c>
-      <c r="AA28">
+      <c r="AH28">
         <v>0.2130269863307577</v>
       </c>
     </row>
@@ -4516,64 +5091,84 @@
         </is>
       </c>
       <c r="J29">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="K29">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="L29">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="M29">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="N29">
+        <v>0.1</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q29">
         <v>0.2130269863307577</v>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q29">
+      <c r="X29">
         <v>-0.03475110777132287</v>
       </c>
-      <c r="R29">
+      <c r="Y29">
         <v>0.9658457778524673</v>
       </c>
-      <c r="S29">
+      <c r="Z29">
         <v>0.0208940689016761</v>
       </c>
-      <c r="T29">
+      <c r="AA29">
         <v>-1.663204421065883</v>
       </c>
-      <c r="U29">
+      <c r="AB29">
         <v>0.1145959988842152</v>
       </c>
-      <c r="V29">
+      <c r="AC29">
         <v>-0.07570273030910638</v>
       </c>
-      <c r="W29">
+      <c r="AD29">
         <v>0.006200514766460642</v>
       </c>
-      <c r="X29">
+      <c r="AE29">
         <v>0.9270917618817148</v>
       </c>
-      <c r="Y29">
+      <c r="AF29">
         <v>1.006219777751038</v>
       </c>
-      <c r="Z29">
+      <c r="AG29">
         <v>-1.396296029967288</v>
       </c>
-      <c r="AA29">
+      <c r="AH29">
         <v>0.214592197779984</v>
       </c>
     </row>
@@ -4620,64 +5215,84 @@
         </is>
       </c>
       <c r="J30">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="K30">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="L30">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="M30">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="N30">
+        <v>0.1</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q30">
         <v>0.3518414027608091</v>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q30">
+      <c r="X30">
         <v>-0.1514253255935879</v>
       </c>
-      <c r="R30">
+      <c r="Y30">
         <v>0.8594820611893771</v>
       </c>
-      <c r="S30">
+      <c r="Z30">
         <v>0.1500586842514219</v>
       </c>
-      <c r="T30">
+      <c r="AA30">
         <v>-1.009107379216228</v>
       </c>
-      <c r="U30">
+      <c r="AB30">
         <v>0.3238937376980864</v>
       </c>
-      <c r="V30">
+      <c r="AC30">
         <v>-0.4455349422938426</v>
       </c>
-      <c r="W30">
+      <c r="AD30">
         <v>0.1426842911066667</v>
       </c>
-      <c r="X30">
+      <c r="AE30">
         <v>0.6404815636979818</v>
       </c>
-      <c r="Y30">
+      <c r="AF30">
         <v>1.15336561639841</v>
       </c>
-      <c r="Z30">
+      <c r="AG30">
         <v>-1.66112279063935</v>
       </c>
-      <c r="AA30">
+      <c r="AH30">
         <v>0.3518414027608091</v>
       </c>
     </row>
@@ -4724,64 +5339,84 @@
         </is>
       </c>
       <c r="J31">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="K31">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="L31">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="M31">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="N31">
+        <v>0.1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q31">
         <v>0.3518414027608091</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>prratio_ln_v</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
         </is>
       </c>
-      <c r="Q31">
+      <c r="X31">
         <v>-0.2242916600288756</v>
       </c>
-      <c r="R31">
+      <c r="Y31">
         <v>0.799082040087989</v>
       </c>
-      <c r="S31">
+      <c r="Z31">
         <v>0.09826985522522132</v>
       </c>
-      <c r="T31">
+      <c r="AA31">
         <v>-2.282405520134626</v>
       </c>
-      <c r="U31">
+      <c r="AB31">
         <v>0.03249341269935009</v>
       </c>
-      <c r="V31">
+      <c r="AC31">
         <v>-0.4168970370362746</v>
       </c>
-      <c r="W31">
+      <c r="AD31">
         <v>-0.03168628302147664</v>
       </c>
-      <c r="X31">
+      <c r="AE31">
         <v>0.659088778184578</v>
       </c>
-      <c r="Y31">
+      <c r="AF31">
         <v>0.9688104667021981</v>
       </c>
-      <c r="Z31">
+      <c r="AG31">
         <v>-4.972052776093125</v>
       </c>
-      <c r="AA31">
+      <c r="AH31">
         <v>0.3794738080197116</v>
       </c>
     </row>
@@ -4792,7 +5427,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4833,22 +5468,57 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -4879,23 +5549,43 @@
       <c r="G2">
         <v>94</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K2">
+        <v>-0.0441289342241922</v>
+      </c>
+      <c r="L2">
+        <v>0.039294877575553</v>
+      </c>
+      <c r="M2">
+        <v>-1.123020020595424</v>
+      </c>
+      <c r="N2">
+        <v>0.2614289916605104</v>
+      </c>
+      <c r="O2">
+        <v>0.1</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R2">
         <v>8.801475483338173E-05</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -4925,23 +5615,43 @@
       <c r="G3">
         <v>28</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K3">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="L3">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="M3">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="N3">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="O3">
+        <v>0.1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="R3">
         <v>0.6896331316971431</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -4971,23 +5681,43 @@
       <c r="G4">
         <v>14</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-0.01623317719789098</v>
+      </c>
+      <c r="L4">
+        <v>0.01085249306634288</v>
+      </c>
+      <c r="M4">
+        <v>-1.495801664986579</v>
+      </c>
+      <c r="N4">
+        <v>0.1347053473598521</v>
+      </c>
+      <c r="O4">
+        <v>0.1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R4">
         <v>0.00152539740558465</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -5017,23 +5747,43 @@
       <c r="G5">
         <v>18</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="L5">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="M5">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="N5">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="O5">
+        <v>0.1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R5">
         <v>0.2130269863307577</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -5063,23 +5813,43 @@
       <c r="G6">
         <v>23</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="L6">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="M6">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="N6">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="O6">
+        <v>0.1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R6">
         <v>0.3518414027608091</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -5114,23 +5884,43 @@
       <c r="G7">
         <v>53</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>peese</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>-0.2280248923827685</v>
+      </c>
+      <c r="L7">
+        <v>0.05623988471185582</v>
+      </c>
+      <c r="M7">
+        <v>-4.054504975446704</v>
+      </c>
+      <c r="N7">
+        <v>5.02405812419616E-05</v>
+      </c>
+      <c r="O7">
+        <v>0.1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R7">
         <v>0.1061267217701378</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -5165,23 +5955,43 @@
       <c r="G8">
         <v>11</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K8">
+        <v>-0.01398931214936958</v>
+      </c>
+      <c r="L8">
+        <v>0.02801957205396191</v>
+      </c>
+      <c r="M8">
+        <v>-0.4992693008454251</v>
+      </c>
+      <c r="N8">
+        <v>0.6175896790784481</v>
+      </c>
+      <c r="O8">
+        <v>0.1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R8">
         <v>0.06140889364563524</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -5216,23 +6026,43 @@
       <c r="G9">
         <v>32</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>-0.01300522048704099</v>
+      </c>
+      <c r="L9">
+        <v>0.02317731125588256</v>
+      </c>
+      <c r="M9">
+        <v>-0.5611186018714822</v>
+      </c>
+      <c r="N9">
+        <v>0.5747166878669911</v>
+      </c>
+      <c r="O9">
+        <v>0.1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R9">
         <v>3.648344743013438E-07</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -5267,23 +6097,43 @@
       <c r="G10">
         <v>23</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>peese</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>-0.2071747835899547</v>
+      </c>
+      <c r="L10">
+        <v>0.1133988387623222</v>
+      </c>
+      <c r="M10">
+        <v>-1.826956835282783</v>
+      </c>
+      <c r="N10">
+        <v>0.0677062596835441</v>
+      </c>
+      <c r="O10">
+        <v>0.1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R10">
         <v>0.8755791713346561</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -5318,23 +6168,43 @@
       <c r="G11">
         <v>13</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>-0.002326701182641406</v>
+      </c>
+      <c r="L11">
+        <v>0.009419121958906233</v>
+      </c>
+      <c r="M11">
+        <v>-0.2470189039692174</v>
+      </c>
+      <c r="N11">
+        <v>0.8048935940809889</v>
+      </c>
+      <c r="O11">
+        <v>0.1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R11">
         <v>0.05791197033513358</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -5369,23 +6239,43 @@
       <c r="G12">
         <v>13</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K12">
+        <v>0.01125249478786305</v>
+      </c>
+      <c r="L12">
+        <v>0.01867213013725901</v>
+      </c>
+      <c r="M12">
+        <v>0.6026358377510148</v>
+      </c>
+      <c r="N12">
+        <v>0.5467509738989856</v>
+      </c>
+      <c r="O12">
+        <v>0.1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R12">
         <v>0.001963325122337626</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -5420,23 +6310,43 @@
       <c r="G13">
         <v>28</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K13">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="L13">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="M13">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="N13">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="O13">
+        <v>0.1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R13">
         <v>0.6896331316971431</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -5471,23 +6381,43 @@
       <c r="G14">
         <v>12</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K14">
+        <v>-0.01562270818073927</v>
+      </c>
+      <c r="L14">
+        <v>0.01140561087549029</v>
+      </c>
+      <c r="M14">
+        <v>-1.369738837427039</v>
+      </c>
+      <c r="N14">
+        <v>0.1707684405789152</v>
+      </c>
+      <c r="O14">
+        <v>0.1</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R14">
         <v>0.009018500526151949</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -5522,23 +6452,43 @@
       <c r="G15">
         <v>18</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K15">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="L15">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="M15">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="N15">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="O15">
+        <v>0.1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R15">
         <v>0.2130269863307577</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -5573,23 +6523,43 @@
       <c r="G16">
         <v>23</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="K16">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="L16">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="M16">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="N16">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="O16">
+        <v>0.1</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R16">
         <v>0.3518414027608091</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>pet</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -5599,7 +6569,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AH16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5650,90 +6620,125 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>bc_estimate</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>pet_status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>peese_status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fit_status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>fit_note</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pet_term</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>model_formula</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>estimate_rr</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>std_error</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>statistic</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>conf_low</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>conf_high</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>conf_low_rr</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>conf_high_rr</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>pet_term_estimate</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pet_term_p_value</t>
         </is>
@@ -5768,74 +6773,94 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J2">
+        <v>-0.0441289342241922</v>
+      </c>
+      <c r="K2">
+        <v>0.039294877575553</v>
+      </c>
+      <c r="L2">
+        <v>-1.123020020595424</v>
+      </c>
+      <c r="M2">
+        <v>0.2614289916605104</v>
+      </c>
+      <c r="N2">
+        <v>0.1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q2">
         <v>8.801475483338173E-05</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q2">
-        <v>-0.09483426427679595</v>
-      </c>
-      <c r="R2">
-        <v>0.9095236625393556</v>
-      </c>
-      <c r="S2">
-        <v>0.04271964348708504</v>
-      </c>
-      <c r="T2">
-        <v>-2.219921716000887</v>
-      </c>
-      <c r="U2">
-        <v>0.02885430705018921</v>
-      </c>
-      <c r="V2">
-        <v>-0.1785632269438737</v>
-      </c>
-      <c r="W2">
-        <v>-0.0111053016097182</v>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X2">
-        <v>0.8364711676898278</v>
+        <v>-0.0441289342241922</v>
       </c>
       <c r="Y2">
-        <v>0.9889561346192752</v>
+        <v>0.956830581310828</v>
       </c>
       <c r="Z2">
-        <v>-6.964456385847269</v>
+        <v>0.03929487743047507</v>
       </c>
       <c r="AA2">
-        <v>0.009633536968474372</v>
+        <v>-1.12302002474165</v>
+      </c>
+      <c r="AB2">
+        <v>0.2643197630713425</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1211454787648392</v>
+      </c>
+      <c r="AD2">
+        <v>0.03288761031645475</v>
+      </c>
+      <c r="AE2">
+        <v>0.8859050698424167</v>
+      </c>
+      <c r="AF2">
+        <v>1.033434385350644</v>
+      </c>
+      <c r="AG2">
+        <v>-2.171136979968024</v>
+      </c>
+      <c r="AH2">
+        <v>8.801475483338173E-05</v>
       </c>
     </row>
     <row r="3">
@@ -5876,64 +6901,84 @@
         </is>
       </c>
       <c r="J3">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="K3">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="L3">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="M3">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="N3">
+        <v>0.1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q3">
         <v>0.6896331316971431</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q3">
+      <c r="X3">
         <v>0.01886571046568258</v>
       </c>
-      <c r="R3">
+      <c r="Y3">
         <v>1.019044792377816</v>
       </c>
-      <c r="S3">
+      <c r="Z3">
         <v>0.04777190240922339</v>
       </c>
-      <c r="T3">
+      <c r="AA3">
         <v>0.3949122709009</v>
       </c>
-      <c r="U3">
+      <c r="AB3">
         <v>0.6960102049424469</v>
       </c>
-      <c r="V3">
+      <c r="AC3">
         <v>-0.07476549772935748</v>
       </c>
-      <c r="W3">
+      <c r="AD3">
         <v>0.1124969186607226</v>
       </c>
-      <c r="X3">
+      <c r="AE3">
         <v>0.9279610697935819</v>
       </c>
-      <c r="Y3">
+      <c r="AF3">
         <v>1.119068808676794</v>
       </c>
-      <c r="Z3">
+      <c r="AG3">
         <v>0.2119180839801686</v>
       </c>
-      <c r="AA3">
+      <c r="AH3">
         <v>0.6896331316971431</v>
       </c>
     </row>
@@ -5966,74 +7011,94 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J4">
+        <v>-0.01623317719789098</v>
+      </c>
+      <c r="K4">
+        <v>0.01085249306634288</v>
+      </c>
+      <c r="L4">
+        <v>-1.495801664986579</v>
+      </c>
+      <c r="M4">
+        <v>0.1347053473598521</v>
+      </c>
+      <c r="N4">
+        <v>0.1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q4">
         <v>0.00152539740558465</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q4">
-        <v>-0.04736005941814025</v>
-      </c>
-      <c r="R4">
-        <v>0.9537439312749914</v>
-      </c>
-      <c r="S4">
-        <v>0.01394608033199637</v>
-      </c>
-      <c r="T4">
-        <v>-3.395940528858311</v>
-      </c>
-      <c r="U4">
-        <v>0.004779457142527119</v>
-      </c>
-      <c r="V4">
-        <v>-0.07469387459435553</v>
-      </c>
-      <c r="W4">
-        <v>-0.02002624424192496</v>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X4">
-        <v>0.9280275356547786</v>
+        <v>-0.01623317719789098</v>
       </c>
       <c r="Y4">
-        <v>0.9801729490731965</v>
+        <v>0.9838978707566386</v>
       </c>
       <c r="Z4">
-        <v>-9.791893465386963</v>
+        <v>0.01085249309360055</v>
       </c>
       <c r="AA4">
-        <v>0.02225205193640684</v>
+        <v>-1.495801661229649</v>
+      </c>
+      <c r="AB4">
+        <v>0.1585823524778318</v>
+      </c>
+      <c r="AC4">
+        <v>-0.03750367280381772</v>
+      </c>
+      <c r="AD4">
+        <v>0.005037318408035753</v>
+      </c>
+      <c r="AE4">
+        <v>0.9631908801031837</v>
+      </c>
+      <c r="AF4">
+        <v>1.005050027026566</v>
+      </c>
+      <c r="AG4">
+        <v>-2.105870116707555</v>
+      </c>
+      <c r="AH4">
+        <v>0.00152539740558465</v>
       </c>
     </row>
     <row r="5">
@@ -6074,64 +7139,84 @@
         </is>
       </c>
       <c r="J5">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="K5">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="L5">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="M5">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="N5">
+        <v>0.1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q5">
         <v>0.2130269863307577</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q5">
+      <c r="X5">
         <v>-0.01650615869253858</v>
       </c>
-      <c r="R5">
+      <c r="Y5">
         <v>0.983629321501455</v>
       </c>
-      <c r="S5">
+      <c r="Z5">
         <v>0.0267672554654336</v>
       </c>
-      <c r="T5">
+      <c r="AA5">
         <v>-0.6166548794609935</v>
       </c>
-      <c r="U5">
+      <c r="AB5">
         <v>0.5456327536525746</v>
       </c>
-      <c r="V5">
+      <c r="AC5">
         <v>-0.06896901536977135</v>
       </c>
-      <c r="W5">
+      <c r="AD5">
         <v>0.03595669798469419</v>
       </c>
-      <c r="X5">
+      <c r="AE5">
         <v>0.9333555993082903</v>
       </c>
-      <c r="Y5">
+      <c r="AF5">
         <v>1.036610958175476</v>
       </c>
-      <c r="Z5">
+      <c r="AG5">
         <v>-0.4058176217004146</v>
       </c>
-      <c r="AA5">
+      <c r="AH5">
         <v>0.2130269863307577</v>
       </c>
     </row>
@@ -6173,64 +7258,84 @@
         </is>
       </c>
       <c r="J6">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="K6">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="L6">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="M6">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="N6">
+        <v>0.1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q6">
         <v>0.3518414027608091</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q6">
+      <c r="X6">
         <v>-0.1514253255935879</v>
       </c>
-      <c r="R6">
+      <c r="Y6">
         <v>0.8594820611893771</v>
       </c>
-      <c r="S6">
+      <c r="Z6">
         <v>0.1500586842514219</v>
       </c>
-      <c r="T6">
+      <c r="AA6">
         <v>-1.009107379216228</v>
       </c>
-      <c r="U6">
+      <c r="AB6">
         <v>0.3238937376980864</v>
       </c>
-      <c r="V6">
+      <c r="AC6">
         <v>-0.4455349422938426</v>
       </c>
-      <c r="W6">
+      <c r="AD6">
         <v>0.1426842911066667</v>
       </c>
-      <c r="X6">
+      <c r="AE6">
         <v>0.6404815636979818</v>
       </c>
-      <c r="Y6">
+      <c r="AF6">
         <v>1.15336561639841</v>
       </c>
-      <c r="Z6">
+      <c r="AG6">
         <v>-1.66112279063935</v>
       </c>
-      <c r="AA6">
+      <c r="AH6">
         <v>0.3518414027608091</v>
       </c>
     </row>
@@ -6268,74 +7373,94 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="J7">
+        <v>-0.2280248923827685</v>
+      </c>
+      <c r="K7">
+        <v>0.05623988471185582</v>
+      </c>
+      <c r="L7">
+        <v>-4.054504975446704</v>
+      </c>
+      <c r="M7">
+        <v>5.02405812419616E-05</v>
+      </c>
+      <c r="N7">
+        <v>0.1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q7">
         <v>0.1061267217701378</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>prratio_ln_se</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
-        </is>
-      </c>
-      <c r="Q7">
-        <v>-0.2280248923827685</v>
-      </c>
-      <c r="R7">
-        <v>0.7961044426522961</v>
-      </c>
-      <c r="S7">
-        <v>0.05623988514012759</v>
-      </c>
-      <c r="T7">
-        <v>-4.054504944571285</v>
-      </c>
-      <c r="U7">
-        <v>0.0001687235753945533</v>
-      </c>
-      <c r="V7">
-        <v>-0.3382530417520879</v>
-      </c>
-      <c r="W7">
-        <v>-0.117796743013449</v>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>prratio_ln_v</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
+        </is>
       </c>
       <c r="X7">
-        <v>0.7130148425441187</v>
+        <v>-0.2598660612944457</v>
       </c>
       <c r="Y7">
-        <v>0.8888767046550042</v>
+        <v>0.7711548663713628</v>
       </c>
       <c r="Z7">
-        <v>-1.018234177038682</v>
+        <v>0.03328198001093026</v>
       </c>
       <c r="AA7">
-        <v>0.1061267217701378</v>
+        <v>-7.80801085780059</v>
+      </c>
+      <c r="AB7">
+        <v>2.562752350564518E-10</v>
+      </c>
+      <c r="AC7">
+        <v>-0.3250975434500509</v>
+      </c>
+      <c r="AD7">
+        <v>-0.1946345791388404</v>
+      </c>
+      <c r="AE7">
+        <v>0.7224568792684545</v>
+      </c>
+      <c r="AF7">
+        <v>0.8231353939495953</v>
+      </c>
+      <c r="AG7">
+        <v>-4.931118471925302</v>
+      </c>
+      <c r="AH7">
+        <v>0.01784479789143678</v>
       </c>
     </row>
     <row r="8">
@@ -6372,74 +7497,94 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J8">
+        <v>-0.01398931214936958</v>
+      </c>
+      <c r="K8">
+        <v>0.02801957205396191</v>
+      </c>
+      <c r="L8">
+        <v>-0.4992693008454251</v>
+      </c>
+      <c r="M8">
+        <v>0.6175896790784481</v>
+      </c>
+      <c r="N8">
+        <v>0.1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q8">
         <v>0.06140889364563524</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q8">
-        <v>-0.04104926192869048</v>
-      </c>
-      <c r="R8">
-        <v>0.959781848078252</v>
-      </c>
-      <c r="S8">
-        <v>0.0414834596191135</v>
-      </c>
-      <c r="T8">
-        <v>-0.9895332333800104</v>
-      </c>
-      <c r="U8">
-        <v>0.3457406751163927</v>
-      </c>
-      <c r="V8">
-        <v>-0.1223553487362746</v>
-      </c>
-      <c r="W8">
-        <v>0.04025682487889364</v>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X8">
-        <v>0.8848338880268932</v>
+        <v>-0.01398931214936958</v>
       </c>
       <c r="Y8">
-        <v>1.041078114621789</v>
+        <v>0.9861080835824433</v>
       </c>
       <c r="Z8">
-        <v>-4.988835520931911</v>
+        <v>0.02801957213560818</v>
       </c>
       <c r="AA8">
-        <v>0.04171936190697131</v>
+        <v>-0.4992692993906037</v>
+      </c>
+      <c r="AB8">
+        <v>0.6283901339179836</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06890666439738365</v>
+      </c>
+      <c r="AD8">
+        <v>0.04092804009864449</v>
+      </c>
+      <c r="AE8">
+        <v>0.9334137967518054</v>
+      </c>
+      <c r="AF8">
+        <v>1.041777136668146</v>
+      </c>
+      <c r="AG8">
+        <v>-1.438915400305928</v>
+      </c>
+      <c r="AH8">
+        <v>0.06140889364563524</v>
       </c>
     </row>
     <row r="9">
@@ -6476,74 +7621,94 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J9">
+        <v>-0.01300522048704099</v>
+      </c>
+      <c r="K9">
+        <v>0.02317731125588256</v>
+      </c>
+      <c r="L9">
+        <v>-0.5611186018714822</v>
+      </c>
+      <c r="M9">
+        <v>0.5747166878669911</v>
+      </c>
+      <c r="N9">
+        <v>0.1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q9">
         <v>3.648344743013438E-07</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q9">
-        <v>-0.05867009048934309</v>
-      </c>
-      <c r="R9">
-        <v>0.9430178283938843</v>
-      </c>
-      <c r="S9">
-        <v>0.03259294229560664</v>
-      </c>
-      <c r="T9">
-        <v>-1.800085735041219</v>
-      </c>
-      <c r="U9">
-        <v>0.08158614487495558</v>
-      </c>
-      <c r="V9">
-        <v>-0.1225510835389243</v>
-      </c>
-      <c r="W9">
-        <v>0.00521090256023813</v>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X9">
-        <v>0.8846607121892646</v>
+        <v>-0.01300522048704099</v>
       </c>
       <c r="Y9">
-        <v>1.005224502926116</v>
+        <v>0.9870789819738031</v>
       </c>
       <c r="Z9">
-        <v>-13.28632606558108</v>
+        <v>0.0231773111185831</v>
       </c>
       <c r="AA9">
-        <v>0.0003475644117808953</v>
+        <v>-0.5611186051954777</v>
+      </c>
+      <c r="AB9">
+        <v>0.578750576522196</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05843191553794361</v>
+      </c>
+      <c r="AD9">
+        <v>0.03242147456386164</v>
+      </c>
+      <c r="AE9">
+        <v>0.9432424583688857</v>
+      </c>
+      <c r="AF9">
+        <v>1.032952776891854</v>
+      </c>
+      <c r="AG9">
+        <v>-2.634695400220785</v>
+      </c>
+      <c r="AH9">
+        <v>3.648344743013438E-07</v>
       </c>
     </row>
     <row r="10">
@@ -6580,74 +7745,94 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>pet</t>
+          <t>peese</t>
         </is>
       </c>
       <c r="J10">
+        <v>-0.2071747835899547</v>
+      </c>
+      <c r="K10">
+        <v>0.1133988387623222</v>
+      </c>
+      <c r="L10">
+        <v>-1.826956835282783</v>
+      </c>
+      <c r="M10">
+        <v>0.0677062596835441</v>
+      </c>
+      <c r="N10">
+        <v>0.1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q10">
         <v>0.8755791713346561</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>prratio_ln_se</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
-        </is>
-      </c>
-      <c r="Q10">
-        <v>-0.2071747835899547</v>
-      </c>
-      <c r="R10">
-        <v>0.8128775599123109</v>
-      </c>
-      <c r="S10">
-        <v>0.1133988387718463</v>
-      </c>
-      <c r="T10">
-        <v>-1.826956835129341</v>
-      </c>
-      <c r="U10">
-        <v>0.08130569386996259</v>
-      </c>
-      <c r="V10">
-        <v>-0.4294324234714377</v>
-      </c>
-      <c r="W10">
-        <v>0.01508285629152831</v>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>prratio_ln_v</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
+        </is>
       </c>
       <c r="X10">
-        <v>0.6508784132154372</v>
+        <v>-0.1992084125040391</v>
       </c>
       <c r="Y10">
-        <v>1.015197176604291</v>
+        <v>0.8193791066851257</v>
       </c>
       <c r="Z10">
-        <v>0.1876542705546367</v>
+        <v>0.07392677096711239</v>
       </c>
       <c r="AA10">
-        <v>0.8755791713346561</v>
+        <v>-2.694672172177796</v>
+      </c>
+      <c r="AB10">
+        <v>0.01323585520137345</v>
+      </c>
+      <c r="AC10">
+        <v>-0.3441022210929207</v>
+      </c>
+      <c r="AD10">
+        <v>-0.05431460391515758</v>
+      </c>
+      <c r="AE10">
+        <v>0.7088564642634092</v>
+      </c>
+      <c r="AF10">
+        <v>0.9471340875331721</v>
+      </c>
+      <c r="AG10">
+        <v>-0.1863456442543887</v>
+      </c>
+      <c r="AH10">
+        <v>0.8903727859390478</v>
       </c>
     </row>
     <row r="11">
@@ -6684,74 +7869,94 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J11">
+        <v>-0.002326701182641406</v>
+      </c>
+      <c r="K11">
+        <v>0.009419121958906233</v>
+      </c>
+      <c r="L11">
+        <v>-0.2470189039692174</v>
+      </c>
+      <c r="M11">
+        <v>0.8048935940809889</v>
+      </c>
+      <c r="N11">
+        <v>0.1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q11">
         <v>0.05791197033513358</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q11">
-        <v>-0.01135694937232996</v>
-      </c>
-      <c r="R11">
-        <v>0.9887072973316636</v>
-      </c>
-      <c r="S11">
-        <v>0.01021621409258023</v>
-      </c>
-      <c r="T11">
-        <v>-1.111659296625177</v>
-      </c>
-      <c r="U11">
-        <v>0.2880608845387202</v>
-      </c>
-      <c r="V11">
-        <v>-0.03138036105213775</v>
-      </c>
-      <c r="W11">
-        <v>0.008666462307477833</v>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X11">
-        <v>0.9691068924473497</v>
+        <v>-0.002326701182641406</v>
       </c>
       <c r="Y11">
-        <v>1.00870412481355</v>
+        <v>0.9976760034884947</v>
       </c>
       <c r="Z11">
-        <v>-8.037711675485626</v>
+        <v>0.009419121996543186</v>
       </c>
       <c r="AA11">
-        <v>0.02518683488334981</v>
+        <v>-0.2470189029821786</v>
+      </c>
+      <c r="AB11">
+        <v>0.8090690395779558</v>
+      </c>
+      <c r="AC11">
+        <v>-0.02078784106185505</v>
+      </c>
+      <c r="AD11">
+        <v>0.01613443869657224</v>
+      </c>
+      <c r="AE11">
+        <v>0.9794267366647682</v>
+      </c>
+      <c r="AF11">
+        <v>1.016265301605157</v>
+      </c>
+      <c r="AG11">
+        <v>-0.948379600560244</v>
+      </c>
+      <c r="AH11">
+        <v>0.05791197033513358</v>
       </c>
     </row>
     <row r="12">
@@ -6788,74 +7993,94 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J12">
+        <v>0.01125249478786305</v>
+      </c>
+      <c r="K12">
+        <v>0.01867213013725901</v>
+      </c>
+      <c r="L12">
+        <v>0.6026358377510148</v>
+      </c>
+      <c r="M12">
+        <v>0.5467509738989856</v>
+      </c>
+      <c r="N12">
+        <v>0.1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q12">
         <v>0.001963325122337626</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q12">
-        <v>-0.06033396056904067</v>
-      </c>
-      <c r="R12">
-        <v>0.9414500738762047</v>
-      </c>
-      <c r="S12">
-        <v>0.01552697325646305</v>
-      </c>
-      <c r="T12">
-        <v>-3.885751561008637</v>
-      </c>
-      <c r="U12">
-        <v>0.002165206649137497</v>
-      </c>
-      <c r="V12">
-        <v>-0.09076626894062485</v>
-      </c>
-      <c r="W12">
-        <v>-0.0299016521974565</v>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X12">
-        <v>0.9132311364371795</v>
+        <v>0.01125249478786305</v>
       </c>
       <c r="Y12">
-        <v>0.9705409794275901</v>
+        <v>1.011316042239452</v>
       </c>
       <c r="Z12">
-        <v>-14.15774432702603</v>
+        <v>0.01867213018063969</v>
       </c>
       <c r="AA12">
-        <v>0.02523944556753687</v>
+        <v>0.6026358363509199</v>
+      </c>
+      <c r="AB12">
+        <v>0.5579679180388102</v>
+      </c>
+      <c r="AC12">
+        <v>-0.02534420788083411</v>
+      </c>
+      <c r="AD12">
+        <v>0.04784919745656022</v>
+      </c>
+      <c r="AE12">
+        <v>0.9749742604406317</v>
+      </c>
+      <c r="AF12">
+        <v>1.049012449650354</v>
+      </c>
+      <c r="AG12">
+        <v>-2.976198166772118</v>
+      </c>
+      <c r="AH12">
+        <v>0.001963325122337626</v>
       </c>
     </row>
     <row r="13">
@@ -6901,64 +8126,84 @@
         </is>
       </c>
       <c r="J13">
+        <v>0.01886571046568258</v>
+      </c>
+      <c r="K13">
+        <v>0.04777190213453326</v>
+      </c>
+      <c r="L13">
+        <v>0.3949122731716596</v>
+      </c>
+      <c r="M13">
+        <v>0.6929076319857237</v>
+      </c>
+      <c r="N13">
+        <v>0.1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q13">
         <v>0.6896331316971431</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q13">
+      <c r="X13">
         <v>0.01886571046568258</v>
       </c>
-      <c r="R13">
+      <c r="Y13">
         <v>1.019044792377816</v>
       </c>
-      <c r="S13">
+      <c r="Z13">
         <v>0.04777190240922339</v>
       </c>
-      <c r="T13">
+      <c r="AA13">
         <v>0.3949122709009</v>
       </c>
-      <c r="U13">
+      <c r="AB13">
         <v>0.6960102049424469</v>
       </c>
-      <c r="V13">
+      <c r="AC13">
         <v>-0.07476549772935748</v>
       </c>
-      <c r="W13">
+      <c r="AD13">
         <v>0.1124969186607226</v>
       </c>
-      <c r="X13">
+      <c r="AE13">
         <v>0.9279610697935819</v>
       </c>
-      <c r="Y13">
+      <c r="AF13">
         <v>1.119068808676794</v>
       </c>
-      <c r="Z13">
+      <c r="AG13">
         <v>0.2119180839801686</v>
       </c>
-      <c r="AA13">
+      <c r="AH13">
         <v>0.6896331316971431</v>
       </c>
     </row>
@@ -6996,74 +8241,94 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="J14">
+        <v>-0.01562270818073927</v>
+      </c>
+      <c r="K14">
+        <v>0.01140561087549029</v>
+      </c>
+      <c r="L14">
+        <v>-1.369738837427039</v>
+      </c>
+      <c r="M14">
+        <v>0.1707684405789152</v>
+      </c>
+      <c r="N14">
+        <v>0.1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q14">
         <v>0.009018500526151949</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>prratio_ln_v</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>prratio_ln ~ 1 + prratio_ln_v | 0</t>
-        </is>
-      </c>
-      <c r="Q14">
-        <v>-0.04417121364231996</v>
-      </c>
-      <c r="R14">
-        <v>0.9567901279257822</v>
-      </c>
-      <c r="S14">
-        <v>0.01182664939555682</v>
-      </c>
-      <c r="T14">
-        <v>-3.734888231227583</v>
-      </c>
-      <c r="U14">
-        <v>0.003295332952781328</v>
-      </c>
-      <c r="V14">
-        <v>-0.06735102051539371</v>
-      </c>
-      <c r="W14">
-        <v>-0.02099140676924621</v>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>prratio_ln_se</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
+        </is>
       </c>
       <c r="X14">
-        <v>0.9348669862436952</v>
+        <v>-0.01562270818073927</v>
       </c>
       <c r="Y14">
-        <v>0.9792273792601353</v>
+        <v>0.9844986932958903</v>
       </c>
       <c r="Z14">
-        <v>-9.163029094789252</v>
+        <v>0.0114056109963859</v>
       </c>
       <c r="AA14">
-        <v>0.04947294756578603</v>
+        <v>-1.369738822908273</v>
+      </c>
+      <c r="AB14">
+        <v>0.1980796049800176</v>
+      </c>
+      <c r="AC14">
+        <v>-0.03797729495532962</v>
+      </c>
+      <c r="AD14">
+        <v>0.006731878593851083</v>
+      </c>
+      <c r="AE14">
+        <v>0.9627347995796776</v>
+      </c>
+      <c r="AF14">
+        <v>1.006754588620332</v>
+      </c>
+      <c r="AG14">
+        <v>-2.053147716251145</v>
+      </c>
+      <c r="AH14">
+        <v>0.009018500526151949</v>
       </c>
     </row>
     <row r="15">
@@ -7109,64 +8374,84 @@
         </is>
       </c>
       <c r="J15">
+        <v>-0.01650615869253858</v>
+      </c>
+      <c r="K15">
+        <v>0.02676725555339267</v>
+      </c>
+      <c r="L15">
+        <v>-0.6166548774346226</v>
+      </c>
+      <c r="M15">
+        <v>0.537462389575474</v>
+      </c>
+      <c r="N15">
+        <v>0.1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q15">
         <v>0.2130269863307577</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q15">
+      <c r="X15">
         <v>-0.01650615869253858</v>
       </c>
-      <c r="R15">
+      <c r="Y15">
         <v>0.983629321501455</v>
       </c>
-      <c r="S15">
+      <c r="Z15">
         <v>0.0267672554654336</v>
       </c>
-      <c r="T15">
+      <c r="AA15">
         <v>-0.6166548794609935</v>
       </c>
-      <c r="U15">
+      <c r="AB15">
         <v>0.5456327536525746</v>
       </c>
-      <c r="V15">
+      <c r="AC15">
         <v>-0.06896901536977135</v>
       </c>
-      <c r="W15">
+      <c r="AD15">
         <v>0.03595669798469419</v>
       </c>
-      <c r="X15">
+      <c r="AE15">
         <v>0.9333555993082903</v>
       </c>
-      <c r="Y15">
+      <c r="AF15">
         <v>1.036610958175476</v>
       </c>
-      <c r="Z15">
+      <c r="AG15">
         <v>-0.4058176217004146</v>
       </c>
-      <c r="AA15">
+      <c r="AH15">
         <v>0.2130269863307577</v>
       </c>
     </row>
@@ -7213,64 +8498,84 @@
         </is>
       </c>
       <c r="J16">
+        <v>-0.1514253255935879</v>
+      </c>
+      <c r="K16">
+        <v>0.1500586848950155</v>
+      </c>
+      <c r="L16">
+        <v>-1.009107374888221</v>
+      </c>
+      <c r="M16">
+        <v>0.3129231414725175</v>
+      </c>
+      <c r="N16">
+        <v>0.1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Q16">
         <v>0.3518414027608091</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>prratio_ln_se</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>prratio_ln ~ 1 + prratio_ln_se | 0</t>
         </is>
       </c>
-      <c r="Q16">
+      <c r="X16">
         <v>-0.1514253255935879</v>
       </c>
-      <c r="R16">
+      <c r="Y16">
         <v>0.8594820611893771</v>
       </c>
-      <c r="S16">
+      <c r="Z16">
         <v>0.1500586842514219</v>
       </c>
-      <c r="T16">
+      <c r="AA16">
         <v>-1.009107379216228</v>
       </c>
-      <c r="U16">
+      <c r="AB16">
         <v>0.3238937376980864</v>
       </c>
-      <c r="V16">
+      <c r="AC16">
         <v>-0.4455349422938426</v>
       </c>
-      <c r="W16">
+      <c r="AD16">
         <v>0.1426842911066667</v>
       </c>
-      <c r="X16">
+      <c r="AE16">
         <v>0.6404815636979818</v>
       </c>
-      <c r="Y16">
+      <c r="AF16">
         <v>1.15336561639841</v>
       </c>
-      <c r="Z16">
+      <c r="AG16">
         <v>-1.66112279063935</v>
       </c>
-      <c r="AA16">
+      <c r="AH16">
         <v>0.3518414027608091</v>
       </c>
     </row>
